--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_第10期_成果指標の仕様_20261014.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_第10期_成果指標の仕様_20261014.xlsx
@@ -3667,7 +3667,7 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第10版_20261014.docx</t>
+          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第11版_20261015.docx</t>
         </is>
       </c>
     </row>
